--- a/Baseline/Physical reservoir computing for digit number/data.xlsx
+++ b/Baseline/Physical reservoir computing for digit number/data.xlsx
@@ -431,22 +431,22 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>digit_0</t>
+          <t>digit_2</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>digit_3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>digit_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>digit_2</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>digit_3</t>
+          <t>digit_0</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -461,12 +461,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>digit_6</t>
+          <t>digit_7</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>digit_7</t>
+          <t>digit_6</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -692,10 +692,10 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
         <v>68.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>5</v>
@@ -820,10 +820,10 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
         <v>141.83</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -930,17 +930,17 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
         <v>141.83</v>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
       <c r="E16" t="n">
         <v>5</v>
       </c>
@@ -948,10 +948,10 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>141.47</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -1029,13 +1029,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>161.61</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>161.61</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
@@ -1044,10 +1044,10 @@
         <v>85.67</v>
       </c>
       <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
         <v>45.16</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
@@ -1061,13 +1061,13 @@
         <v>204.9</v>
       </c>
       <c r="B20" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="C20" t="n">
         <v>85.67</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>204.9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>251.4</v>
       </c>
       <c r="E20" t="n">
         <v>45.16</v>
@@ -1076,10 +1076,10 @@
         <v>251.4</v>
       </c>
       <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
         <v>110.98</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>45.16</v>
@@ -1093,13 +1093,13 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>118.98</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="B23" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
         <v>45.16</v>
-      </c>
-      <c r="B23" t="n">
-        <v>5</v>
-      </c>
-      <c r="C23" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="D23" t="n">
-        <v>175.4</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -1172,10 +1172,10 @@
         <v>175.4</v>
       </c>
       <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
         <v>85.67</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
       </c>
       <c r="I23" t="n">
         <v>85.67</v>
@@ -1186,16 +1186,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="B24" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>161.61</v>
+      </c>
+      <c r="D24" t="n">
         <v>194.09</v>
-      </c>
-      <c r="B24" t="n">
-        <v>161.61</v>
-      </c>
-      <c r="C24" t="n">
-        <v>204.9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>251.4</v>
       </c>
       <c r="E24" t="n">
         <v>45.16</v>
@@ -1204,10 +1204,10 @@
         <v>141.47</v>
       </c>
       <c r="G24" t="n">
-        <v>118.98</v>
+        <v>175.4</v>
       </c>
       <c r="H24" t="n">
-        <v>175.4</v>
+        <v>118.98</v>
       </c>
       <c r="I24" t="n">
         <v>251.4</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
@@ -1282,16 +1282,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>161.61</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
         <v>85.67</v>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="n">
-        <v>161.61</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>151.72</v>
+      </c>
+      <c r="B28" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="C28" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="D28" t="n">
         <v>194.09</v>
-      </c>
-      <c r="B28" t="n">
-        <v>113.61</v>
-      </c>
-      <c r="C28" t="n">
-        <v>151.72</v>
-      </c>
-      <c r="D28" t="n">
-        <v>85.67</v>
       </c>
       <c r="E28" t="n">
         <v>45.16</v>
@@ -1332,10 +1332,10 @@
         <v>68.25</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>251.4</v>
       </c>
       <c r="H28" t="n">
-        <v>251.4</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>171.72</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="C29" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="H29" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>5</v>
@@ -1416,10 +1416,10 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
         <v>161.61</v>
-      </c>
-      <c r="D31" t="n">
-        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>5</v>
@@ -1428,10 +1428,10 @@
         <v>58.28</v>
       </c>
       <c r="G31" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="H31" t="n">
         <v>113.61</v>
-      </c>
-      <c r="H31" t="n">
-        <v>175.4</v>
       </c>
       <c r="I31" t="n">
         <v>113.61</v>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="B32" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="C32" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="D32" t="n">
         <v>104.65</v>
-      </c>
-      <c r="B32" t="n">
-        <v>85.78</v>
-      </c>
-      <c r="C32" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="D32" t="n">
-        <v>85.67</v>
       </c>
       <c r="E32" t="n">
         <v>45.16</v>
@@ -1460,10 +1460,10 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>85.67</v>
       </c>
       <c r="H32" t="n">
-        <v>85.67</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
         <v>161.61</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="C33" t="n">
         <v>5</v>
@@ -1492,10 +1492,10 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="H33" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
         <v>5</v>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
         <v>141.83</v>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="n">
-        <v>5</v>
       </c>
       <c r="E35" t="n">
         <v>5</v>
@@ -1556,10 +1556,10 @@
         <v>85.67</v>
       </c>
       <c r="G35" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="H35" t="n">
         <v>141.83</v>
-      </c>
-      <c r="H35" t="n">
-        <v>204.9</v>
       </c>
       <c r="I35" t="n">
         <v>85.67</v>
@@ -1570,16 +1570,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="B36" t="n">
+        <v>161.61</v>
+      </c>
+      <c r="C36" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="D36" t="n">
         <v>45.16</v>
-      </c>
-      <c r="B36" t="n">
-        <v>141.47</v>
-      </c>
-      <c r="C36" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="D36" t="n">
-        <v>161.61</v>
       </c>
       <c r="E36" t="n">
         <v>85.67</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E37" t="n">
         <v>5</v>
@@ -1652,10 +1652,10 @@
         <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="H38" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
         <v>5</v>
@@ -1666,16 +1666,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>85.89</v>
+        <v>45.16</v>
       </c>
       <c r="B39" t="n">
-        <v>45.16</v>
+        <v>161.61</v>
       </c>
       <c r="C39" t="n">
         <v>45.16</v>
       </c>
       <c r="D39" t="n">
-        <v>161.61</v>
+        <v>85.89</v>
       </c>
       <c r="E39" t="n">
         <v>5</v>
@@ -1684,10 +1684,10 @@
         <v>45.16</v>
       </c>
       <c r="G39" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="H39" t="n">
         <v>141.83</v>
-      </c>
-      <c r="H39" t="n">
-        <v>110.98</v>
       </c>
       <c r="I39" t="n">
         <v>85.67</v>
@@ -1698,16 +1698,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="B40" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="D40" t="n">
         <v>45.16</v>
-      </c>
-      <c r="B40" t="n">
-        <v>110.98</v>
-      </c>
-      <c r="C40" t="n">
-        <v>204.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>204.9</v>
       </c>
       <c r="E40" t="n">
         <v>113.61</v>
@@ -1716,10 +1716,10 @@
         <v>110.98</v>
       </c>
       <c r="G40" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="H40" t="n">
         <v>175.4</v>
-      </c>
-      <c r="H40" t="n">
-        <v>113.61</v>
       </c>
       <c r="I40" t="n">
         <v>141.47</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B41" t="n">
         <v>5</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
@@ -1748,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="B43" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D43" t="n">
         <v>110.98</v>
-      </c>
-      <c r="B43" t="n">
-        <v>45.16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="D43" t="n">
-        <v>175.4</v>
       </c>
       <c r="E43" t="n">
         <v>85.67</v>
@@ -1812,10 +1812,10 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="H43" t="n">
         <v>85.78</v>
-      </c>
-      <c r="H43" t="n">
-        <v>118.98</v>
       </c>
       <c r="I43" t="n">
         <v>85.67</v>
@@ -1826,16 +1826,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="B44" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D44" t="n">
         <v>45.16</v>
-      </c>
-      <c r="B44" t="n">
-        <v>118.98</v>
-      </c>
-      <c r="C44" t="n">
-        <v>204.9</v>
-      </c>
-      <c r="D44" t="n">
-        <v>204.9</v>
       </c>
       <c r="E44" t="n">
         <v>204.9</v>
@@ -1844,10 +1844,10 @@
         <v>141.47</v>
       </c>
       <c r="G44" t="n">
+        <v>141.83</v>
+      </c>
+      <c r="H44" t="n">
         <v>194.09</v>
-      </c>
-      <c r="H44" t="n">
-        <v>141.83</v>
       </c>
       <c r="I44" t="n">
         <v>110.98</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
         <v>5</v>
@@ -1867,7 +1867,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E45" t="n">
         <v>5</v>
@@ -1876,10 +1876,10 @@
         <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="I45" t="n">
         <v>5</v>
@@ -1922,16 +1922,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="B47" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="C47" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="D47" t="n">
         <v>110.98</v>
-      </c>
-      <c r="B47" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="C47" t="n">
-        <v>113.61</v>
-      </c>
-      <c r="D47" t="n">
-        <v>68.25</v>
       </c>
       <c r="E47" t="n">
         <v>141.47</v>
@@ -1940,10 +1940,10 @@
         <v>5</v>
       </c>
       <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
         <v>151.18</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5</v>
       </c>
       <c r="I47" t="n">
         <v>161.61</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="B48" t="n">
+        <v>141.83</v>
+      </c>
+      <c r="C48" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D48" t="n">
         <v>45.16</v>
-      </c>
-      <c r="B48" t="n">
-        <v>118.98</v>
-      </c>
-      <c r="C48" t="n">
-        <v>204.9</v>
-      </c>
-      <c r="D48" t="n">
-        <v>141.83</v>
       </c>
       <c r="E48" t="n">
         <v>58.28</v>
@@ -1972,10 +1972,10 @@
         <v>113.61</v>
       </c>
       <c r="G48" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="H48" t="n">
         <v>171.72</v>
-      </c>
-      <c r="H48" t="n">
-        <v>110.98</v>
       </c>
       <c r="I48" t="n">
         <v>118.98</v>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="B49" t="n">
         <v>5</v>
@@ -1995,7 +1995,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E49" t="n">
         <v>5</v>
@@ -2050,16 +2050,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118.98</v>
+        <v>141.47</v>
       </c>
       <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="n">
         <v>85.67</v>
       </c>
-      <c r="C51" t="n">
-        <v>141.47</v>
-      </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E51" t="n">
         <v>5</v>
@@ -2068,10 +2068,10 @@
         <v>5</v>
       </c>
       <c r="G51" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="H51" t="n">
         <v>151.18</v>
-      </c>
-      <c r="H51" t="n">
-        <v>45.16</v>
       </c>
       <c r="I51" t="n">
         <v>161.61</v>
@@ -2082,16 +2082,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="B52" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="C52" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="D52" t="n">
         <v>85.67</v>
-      </c>
-      <c r="B52" t="n">
-        <v>118.98</v>
-      </c>
-      <c r="C52" t="n">
-        <v>251.4</v>
-      </c>
-      <c r="D52" t="n">
-        <v>113.61</v>
       </c>
       <c r="E52" t="n">
         <v>113.61</v>
@@ -2100,10 +2100,10 @@
         <v>113.61</v>
       </c>
       <c r="G52" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="H52" t="n">
         <v>157.45</v>
-      </c>
-      <c r="H52" t="n">
-        <v>110.98</v>
       </c>
       <c r="I52" t="n">
         <v>118.98</v>
@@ -2114,13 +2114,13 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="B53" t="n">
         <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
         <v>5</v>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="B54" t="n">
         <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>5</v>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118.98</v>
+        <v>144.5</v>
       </c>
       <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
         <v>161.61</v>
       </c>
-      <c r="C55" t="n">
-        <v>144.5</v>
-      </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="E55" t="n">
         <v>5</v>
@@ -2196,10 +2196,10 @@
         <v>5</v>
       </c>
       <c r="G55" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="H55" t="n">
         <v>203.96</v>
-      </c>
-      <c r="H55" t="n">
-        <v>45.16</v>
       </c>
       <c r="I55" t="n">
         <v>85.78</v>
@@ -2210,13 +2210,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="B56" t="n">
         <v>113.61</v>
       </c>
-      <c r="B56" t="n">
-        <v>5</v>
-      </c>
       <c r="C56" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>113.61</v>
@@ -2228,10 +2228,10 @@
         <v>204.9</v>
       </c>
       <c r="G56" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="H56" t="n">
         <v>141.47</v>
-      </c>
-      <c r="H56" t="n">
-        <v>110.98</v>
       </c>
       <c r="I56" t="n">
         <v>118.98</v>
@@ -2242,13 +2242,13 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5</v>
+        <v>141.47</v>
       </c>
       <c r="B57" t="n">
         <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>141.47</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
         <v>5</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="C58" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
         <v>5</v>
@@ -2306,16 +2306,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="B59" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="C59" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="D59" t="n">
         <v>151.18</v>
-      </c>
-      <c r="B59" t="n">
-        <v>113.61</v>
-      </c>
-      <c r="C59" t="n">
-        <v>251.4</v>
-      </c>
-      <c r="D59" t="n">
-        <v>118.98</v>
       </c>
       <c r="E59" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
         <v>85.67</v>
       </c>
       <c r="G59" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="H59" t="n">
         <v>175.4</v>
-      </c>
-      <c r="H59" t="n">
-        <v>85.67</v>
       </c>
       <c r="I59" t="n">
         <v>151.18</v>
@@ -2338,16 +2338,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>141.83</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
         <v>141.47</v>
-      </c>
-      <c r="B60" t="n">
-        <v>5</v>
-      </c>
-      <c r="C60" t="n">
-        <v>5</v>
-      </c>
-      <c r="D60" t="n">
-        <v>141.83</v>
       </c>
       <c r="E60" t="n">
         <v>113.61</v>
@@ -2356,10 +2356,10 @@
         <v>141.47</v>
       </c>
       <c r="G60" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="H60" t="n">
         <v>110.98</v>
-      </c>
-      <c r="H60" t="n">
-        <v>118.98</v>
       </c>
       <c r="I60" t="n">
         <v>118.98</v>
@@ -2402,16 +2402,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="C62" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
         <v>5</v>
@@ -2434,13 +2434,13 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="B63" t="n">
         <v>251.4</v>
       </c>
-      <c r="B63" t="n">
+      <c r="C63" t="n">
         <v>141.83</v>
-      </c>
-      <c r="C63" t="n">
-        <v>141.47</v>
       </c>
       <c r="D63" t="n">
         <v>251.4</v>
@@ -2452,10 +2452,10 @@
         <v>161.61</v>
       </c>
       <c r="G63" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="H63" t="n">
         <v>161.61</v>
-      </c>
-      <c r="H63" t="n">
-        <v>85.67</v>
       </c>
       <c r="I63" t="n">
         <v>203.96</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="n">
         <v>110.98</v>
-      </c>
-      <c r="B64" t="n">
-        <v>5</v>
-      </c>
-      <c r="C64" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" t="n">
-        <v>141.47</v>
       </c>
       <c r="E64" t="n">
         <v>113.61</v>
@@ -2484,10 +2484,10 @@
         <v>118.98</v>
       </c>
       <c r="G64" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="I64" t="n">
         <v>118.98</v>
@@ -2533,13 +2533,13 @@
         <v>5</v>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>45.16</v>
       </c>
       <c r="C66" t="n">
         <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>45.16</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>5</v>
@@ -2562,13 +2562,13 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
+        <v>5</v>
+      </c>
+      <c r="B67" t="n">
         <v>251.4</v>
       </c>
-      <c r="B67" t="n">
+      <c r="C67" t="n">
         <v>141.83</v>
-      </c>
-      <c r="C67" t="n">
-        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>251.4</v>
@@ -2580,10 +2580,10 @@
         <v>251.4</v>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>113.61</v>
       </c>
       <c r="H67" t="n">
-        <v>113.61</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
         <v>204.9</v>
@@ -2597,13 +2597,13 @@
         <v>5</v>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>118.98</v>
       </c>
       <c r="C68" t="n">
         <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>118.98</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
         <v>113.61</v>
@@ -2693,13 +2693,13 @@
         <v>5</v>
       </c>
       <c r="B71" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="C71" t="n">
         <v>68.25</v>
       </c>
-      <c r="C71" t="n">
-        <v>5</v>
-      </c>
       <c r="D71" t="n">
-        <v>204.9</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
         <v>5</v>
@@ -2708,10 +2708,10 @@
         <v>141.47</v>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>141.83</v>
       </c>
       <c r="H71" t="n">
-        <v>141.83</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
         <v>141.83</v>
@@ -2836,10 +2836,10 @@
         <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>5</v>
+        <v>85.78</v>
       </c>
       <c r="H75" t="n">
-        <v>85.78</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
